--- a/updatedMemberData.xlsx
+++ b/updatedMemberData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madmarshall/Documents/medicaidOversightMap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BD0D06-82C2-EF45-8B5A-FBC27D05E168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB0BD0E-7263-EC42-BB7D-4AA520EB14B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="660" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7100" yWindow="660" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="494">
   <si>
     <t>Oversight?</t>
   </si>
@@ -1499,6 +1499,27 @@
   </si>
   <si>
     <t>Louisiana</t>
+  </si>
+  <si>
+    <t>https://www.dpbh.nv.gov/about/organizational-charts/</t>
+  </si>
+  <si>
+    <t>https://health.mo.gov/about/pdf/org-chart-ada.pdf</t>
+  </si>
+  <si>
+    <t>https://www.nmhealth.org/about/</t>
+  </si>
+  <si>
+    <t>https://dph.sc.gov/sites/scdph/files/Library/00029-ENG-CR.pdf</t>
+  </si>
+  <si>
+    <t>https://dph.georgia.gov/about-dph</t>
+  </si>
+  <si>
+    <t>https://www.chfs.ky.gov/agencies/Pages/default.aspx</t>
+  </si>
+  <si>
+    <t>https://www.tn.gov/health/dept.html</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1696,23 +1717,15 @@
     <xf numFmtId="22" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="22" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1853,21 +1866,21 @@
     <sortCondition descending="1" ref="A1:A58"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="24" xr3:uid="{EC3A8AE4-1AEA-44FE-9DAE-C845A25235D5}" name="Oversight?" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{80BFFD16-634B-644C-BC67-0E0C16458147}" name="jurisdictionName" dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{EC3A8AE4-1AEA-44FE-9DAE-C845A25235D5}" name="Oversight?" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{80BFFD16-634B-644C-BC67-0E0C16458147}" name="jurisdictionName" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Account Name"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Agency Structure"/>
-    <tableColumn id="23" xr3:uid="{091B2DD4-B1BA-4A29-9F94-96F9DC3BAAB3}" name="Public Health Website" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="25" xr3:uid="{AF3B510E-B66B-4682-A68A-7103145FD741}" name="HHS or Medicaid Context " dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Governor Term Year" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Acronym" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{091B2DD4-B1BA-4A29-9F94-96F9DC3BAAB3}" name="Public Health Website" dataDxfId="11" dataCellStyle="Hyperlink"/>
+    <tableColumn id="25" xr3:uid="{AF3B510E-B66B-4682-A68A-7103145FD741}" name="HHS or Medicaid Context " dataDxfId="10" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Governor Term Year" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Acronym" dataDxfId="8"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Governance Classification"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="S/THO"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="S/THO Designee"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="S/THO Acting"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="S/THO Assistant"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="City"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Org Chart" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Org Chart" dataDxfId="7"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Secretary of Health"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Population"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="PHAB Accreditation"/>
@@ -1886,21 +1899,21 @@
     <sortCondition ref="C1:C58"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="24" xr3:uid="{14C78B0C-CC4B-CF46-9A7C-80025A9DF37D}" name="Oversight?" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{6CBE6995-E45E-3049-8744-E0D6CCBBA85B}" name="jurisdictionName" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{14C78B0C-CC4B-CF46-9A7C-80025A9DF37D}" name="Oversight?" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{6CBE6995-E45E-3049-8744-E0D6CCBBA85B}" name="jurisdictionName" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{ABF7AE7E-A482-594D-A5CB-B4905C32B62F}" name="Account Name"/>
     <tableColumn id="8" xr3:uid="{BF737C6C-A012-604E-A01C-BCFB91745840}" name="Agency Structure"/>
-    <tableColumn id="23" xr3:uid="{608D6F1D-623F-1C46-A561-376D2FF08802}" name="Public Health Website" dataDxfId="11" dataCellStyle="Hyperlink"/>
-    <tableColumn id="25" xr3:uid="{7589D836-3A5F-7245-BA28-2ECAE78D012C}" name="HHS or Medicaid Context " dataDxfId="10" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{95DCC688-5259-4A49-930B-C3CC0DEC12A1}" name="Governor Term Year" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{0204E4C1-D1DD-544F-8D61-3FF5C9921AA5}" name="Acronym" dataDxfId="8"/>
+    <tableColumn id="23" xr3:uid="{608D6F1D-623F-1C46-A561-376D2FF08802}" name="Public Health Website" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="25" xr3:uid="{7589D836-3A5F-7245-BA28-2ECAE78D012C}" name="HHS or Medicaid Context " dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{95DCC688-5259-4A49-930B-C3CC0DEC12A1}" name="Governor Term Year" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{0204E4C1-D1DD-544F-8D61-3FF5C9921AA5}" name="Acronym" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{ACCB8137-D23C-A946-8E75-567466A7F46C}" name="Governance Classification"/>
     <tableColumn id="10" xr3:uid="{7DCBF5BA-5DF1-0047-AE0D-A6E10097AAEC}" name="S/THO"/>
     <tableColumn id="11" xr3:uid="{1A2764D9-A525-1B44-B6ED-2AA6B8858981}" name="S/THO Designee"/>
     <tableColumn id="12" xr3:uid="{A681CC24-8158-CD49-8463-FE64CB9B7E72}" name="S/THO Acting"/>
     <tableColumn id="13" xr3:uid="{AD1D389E-A518-B442-8CA6-24244C29E7BB}" name="S/THO Assistant"/>
     <tableColumn id="14" xr3:uid="{4329E990-607A-A842-94A4-0B9A7726AEFA}" name="City"/>
-    <tableColumn id="15" xr3:uid="{95704B20-B1E8-5E4D-BE79-A10A24760E8F}" name="Org Chart" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{95704B20-B1E8-5E4D-BE79-A10A24760E8F}" name="Org Chart" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{C1E947F7-D643-6B4D-8B70-FCF6D199B1B7}" name="Secretary of Health"/>
     <tableColumn id="17" xr3:uid="{AB12B992-E9C8-5143-B983-304420EB6603}" name="Population"/>
     <tableColumn id="18" xr3:uid="{4DBDC531-DAC6-5E48-8329-7F795ECC5EBD}" name="PHAB Accreditation"/>
@@ -2237,6 +2250,7 @@
     <col min="3" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="5" width="37.83203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="30" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="26.33203125" customWidth="1"/>
     <col min="9" max="9" width="23.5" style="1" customWidth="1"/>
     <col min="10" max="13" width="14" style="1" customWidth="1"/>
@@ -2328,7 +2342,7 @@
         <v>260</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>311</v>
+        <v>492</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="1" t="s">
@@ -2378,7 +2392,7 @@
       <c r="A3" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="24" t="s">
         <v>453</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2387,11 +2401,11 @@
       <c r="D3" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="29" t="s">
         <v>336</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -2438,7 +2452,7 @@
       <c r="A4" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="24" t="s">
         <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2447,11 +2461,11 @@
       <c r="D4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="29" t="s">
         <v>349</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -2602,7 +2616,7 @@
       <c r="A7" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="24" t="s">
         <v>469</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2999,10 +3013,10 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>457</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -3056,7 +3070,7 @@
       <c r="A15" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="24" t="s">
         <v>459</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3066,7 +3080,7 @@
         <v>260</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>355</v>
+        <v>487</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="1" t="s">
@@ -3114,7 +3128,7 @@
       <c r="A16" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="24" t="s">
         <v>460</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -3171,7 +3185,7 @@
       <c r="A17" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="24" t="s">
         <v>464</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -3228,7 +3242,7 @@
       <c r="A18" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="24" t="s">
         <v>466</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -3278,7 +3292,7 @@
       <c r="A19" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="24" t="s">
         <v>474</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -3335,7 +3349,7 @@
       <c r="A20" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="24" t="s">
         <v>483</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3389,7 +3403,7 @@
       <c r="A21" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="24" t="s">
         <v>484</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -3448,7 +3462,7 @@
       <c r="A22" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="24" t="s">
         <v>485</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -3507,7 +3521,7 @@
       <c r="A23" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="24" t="s">
         <v>472</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3555,7 +3569,7 @@
       <c r="A24" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="24" t="s">
         <v>473</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -4068,7 +4082,9 @@
       <c r="D33" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="1"/>
+      <c r="E33" s="4" t="s">
+        <v>491</v>
+      </c>
       <c r="F33" s="8"/>
       <c r="G33" s="1" t="s">
         <v>24</v>
@@ -4395,7 +4411,7 @@
       <c r="A39" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="24" t="s">
         <v>454</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -4452,7 +4468,7 @@
       <c r="A40" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="24" t="s">
         <v>455</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -4509,7 +4525,7 @@
       <c r="A41" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="24" t="s">
         <v>456</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -4519,7 +4535,7 @@
         <v>22</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>127</v>
+        <v>488</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1" t="s">
@@ -4563,7 +4579,7 @@
       <c r="A42" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="24" t="s">
         <v>461</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -4620,7 +4636,7 @@
       <c r="A43" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="24" t="s">
         <v>462</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -4630,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="1" t="s">
@@ -4680,7 +4696,7 @@
       <c r="A44" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="24" t="s">
         <v>463</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -4734,7 +4750,7 @@
       <c r="A45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="24" t="s">
         <v>465</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -4791,7 +4807,7 @@
       <c r="A46" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="24" t="s">
         <v>467</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -4848,7 +4864,7 @@
       <c r="A47" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="24" t="s">
         <v>468</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -4902,7 +4918,7 @@
       <c r="A48" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="24" t="s">
         <v>470</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -4959,7 +4975,7 @@
       <c r="A49" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="24" t="s">
         <v>471</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -5009,7 +5025,7 @@
       <c r="A50" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="24" t="s">
         <v>475</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -5019,7 +5035,7 @@
         <v>22</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>179</v>
+        <v>490</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="1" t="s">
@@ -5069,7 +5085,7 @@
       <c r="A51" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="24" t="s">
         <v>476</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -5126,7 +5142,7 @@
       <c r="A52" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="24" t="s">
         <v>477</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -5135,7 +5151,9 @@
       <c r="D52" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="1"/>
+      <c r="E52" s="4" t="s">
+        <v>493</v>
+      </c>
       <c r="F52" s="8"/>
       <c r="G52" s="1" t="s">
         <v>24</v>
@@ -5175,7 +5193,7 @@
       <c r="A53" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="24" t="s">
         <v>478</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -5230,7 +5248,7 @@
       <c r="A54" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="24" t="s">
         <v>479</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -5283,7 +5301,7 @@
       <c r="A55" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="24" t="s">
         <v>480</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -5340,7 +5358,7 @@
       <c r="A56" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="24" t="s">
         <v>481</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -5399,7 +5417,7 @@
       <c r="A57" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="24" t="s">
         <v>482</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -5456,7 +5474,7 @@
       <c r="A58" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="24" t="s">
         <v>69</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -5509,56 +5527,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="32"/>
-      <c r="B59" s="33"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="22"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="22"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="22"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="22"/>
-    </row>
-    <row r="60" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="34"/>
-      <c r="B60" s="33"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="22"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="22"/>
-    </row>
-    <row r="61" spans="1:21" s="21" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="35"/>
-      <c r="B61" s="33"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="22"/>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" s="26"/>
+      <c r="E59" s="25"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A60" s="27"/>
+      <c r="E60" s="25"/>
+    </row>
+    <row r="61" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="28"/>
+      <c r="E61" s="25"/>
     </row>
   </sheetData>
   <dataValidations xWindow="185" yWindow="923" count="12">
@@ -5655,51 +5634,53 @@
     <hyperlink ref="E34" r:id="rId64" xr:uid="{3D68E0F6-565A-4E31-8041-14A4E4AAA026}"/>
     <hyperlink ref="E5" r:id="rId65" xr:uid="{EF1D420F-18EF-4E76-89A3-98850C9AF20C}"/>
     <hyperlink ref="E35" r:id="rId66" xr:uid="{F78DA305-9BB5-4F2E-B4F8-66EC8FBDDA3D}"/>
-    <hyperlink ref="E11" r:id="rId67" xr:uid="{8F612C67-B290-475F-A329-18B4A1CD494F}"/>
-    <hyperlink ref="E36" r:id="rId68" xr:uid="{34B32381-DA3D-48A1-8F3A-7BA553623903}"/>
-    <hyperlink ref="E37" r:id="rId69" xr:uid="{45465AA5-EEE0-48FC-9065-53047723500D}"/>
-    <hyperlink ref="E38" r:id="rId70" xr:uid="{13BB9942-A405-4DA2-8E06-01F90B4BD748}"/>
-    <hyperlink ref="E6" r:id="rId71" xr:uid="{DA4BEBE2-080E-4CD9-B20D-9A66E0B9BA0E}"/>
-    <hyperlink ref="E2" r:id="rId72" xr:uid="{2A421EFC-5CE1-4915-BCFF-E0F180BC7805}"/>
-    <hyperlink ref="E12" r:id="rId73" xr:uid="{9BAD52EC-0FBB-47D0-B299-98976A4A44C1}"/>
-    <hyperlink ref="E13" r:id="rId74" xr:uid="{BBB29648-EE03-4690-B8CF-7336712FAED6}"/>
-    <hyperlink ref="E3" r:id="rId75" xr:uid="{02DC2D59-84BF-4EEB-AE0B-79A2F174ED4E}"/>
-    <hyperlink ref="E39" r:id="rId76" xr:uid="{A63C04C4-8DD9-435D-ABF9-0203E47DF1B0}"/>
-    <hyperlink ref="E40" r:id="rId77" xr:uid="{8E647A81-A99D-4893-8BBE-EA2D0B10E098}"/>
-    <hyperlink ref="E41" r:id="rId78" xr:uid="{C9CED6DD-2DA0-41FC-871A-F66D82DD880B}"/>
-    <hyperlink ref="E14" r:id="rId79" xr:uid="{2E33A0D8-379C-435E-914F-1511B519A04E}"/>
-    <hyperlink ref="E4" r:id="rId80" xr:uid="{28D87A6B-7FF4-40B3-B258-618F4D30BC9B}"/>
-    <hyperlink ref="E15" r:id="rId81" xr:uid="{25D99204-4613-42A1-BE9B-F2E5D561C894}"/>
-    <hyperlink ref="E16" r:id="rId82" xr:uid="{EB604F45-7F62-4D95-87A0-7C607F70EEE6}"/>
-    <hyperlink ref="E42" r:id="rId83" xr:uid="{FF0F238A-0D26-48C4-A15F-7954889B76EF}"/>
-    <hyperlink ref="E43" r:id="rId84" xr:uid="{60B932FB-29EC-45F2-B889-1CB79A7CA2CB}"/>
-    <hyperlink ref="E44" r:id="rId85" xr:uid="{6A9F5AC2-0769-4F65-A1B3-C7B6B78865CF}"/>
-    <hyperlink ref="E17" r:id="rId86" xr:uid="{8F8CC71E-CB4F-469E-8417-A15A6E522D48}"/>
-    <hyperlink ref="E45" r:id="rId87" xr:uid="{70588B6D-86C2-4E9D-A653-EB43F4458978}"/>
-    <hyperlink ref="E18" r:id="rId88" xr:uid="{2BC13BFC-19BE-477A-82E0-7D14CED900F5}"/>
-    <hyperlink ref="E46" r:id="rId89" xr:uid="{7A331BB3-C033-4479-BE55-986C3D9F9A53}"/>
-    <hyperlink ref="E47" r:id="rId90" xr:uid="{9D770BB2-4EC1-4C1B-9178-82ADFA28631B}"/>
-    <hyperlink ref="E7" r:id="rId91" xr:uid="{9BCD1D34-3807-4EFF-9AFB-1B2D272BAC40}"/>
-    <hyperlink ref="E48" r:id="rId92" xr:uid="{D7E4C853-E250-43E6-9D4D-F09FCBFF6B2F}"/>
-    <hyperlink ref="E49" r:id="rId93" xr:uid="{74D7670D-4811-4714-AC93-1B08F70715DA}"/>
-    <hyperlink ref="E19" r:id="rId94" xr:uid="{CB748B89-0123-4681-825A-E27A0BE8ECB1}"/>
-    <hyperlink ref="E50" r:id="rId95" xr:uid="{A29855BD-159B-419E-AEF2-13C042924D47}"/>
-    <hyperlink ref="E51" r:id="rId96" xr:uid="{4D3EFA2A-19FF-4AD8-84E1-C8E13C595478}"/>
-    <hyperlink ref="E53" r:id="rId97" xr:uid="{A4C956F3-167F-4BD7-A91C-26AD208A0BD1}"/>
-    <hyperlink ref="E54" r:id="rId98" xr:uid="{1749D594-EE49-4E34-B8D1-987FAE0B65C9}"/>
-    <hyperlink ref="E56" r:id="rId99" xr:uid="{1380FF99-EF25-4839-8AF5-637A67A7D467}"/>
-    <hyperlink ref="E57" r:id="rId100" xr:uid="{4E15A300-DD30-44C2-BA8F-B49EEC02963B}"/>
-    <hyperlink ref="E58" r:id="rId101" xr:uid="{0F99CB0B-4B4B-4B69-9AC3-D56535324B5D}"/>
-    <hyperlink ref="E20" r:id="rId102" xr:uid="{D941B546-8A6E-4F9C-AEA8-DF3FB2FD1934}"/>
-    <hyperlink ref="E21" r:id="rId103" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
-    <hyperlink ref="E22" r:id="rId104" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
-    <hyperlink ref="F56" r:id="rId105" xr:uid="{435B592D-DD21-4EC5-9AFF-18B7F3BB085D}"/>
-    <hyperlink ref="F22" r:id="rId106" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
-    <hyperlink ref="F21" r:id="rId107" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
+    <hyperlink ref="E36" r:id="rId67" xr:uid="{34B32381-DA3D-48A1-8F3A-7BA553623903}"/>
+    <hyperlink ref="E37" r:id="rId68" xr:uid="{45465AA5-EEE0-48FC-9065-53047723500D}"/>
+    <hyperlink ref="E38" r:id="rId69" xr:uid="{13BB9942-A405-4DA2-8E06-01F90B4BD748}"/>
+    <hyperlink ref="E6" r:id="rId70" xr:uid="{DA4BEBE2-080E-4CD9-B20D-9A66E0B9BA0E}"/>
+    <hyperlink ref="E2" r:id="rId71" xr:uid="{2A421EFC-5CE1-4915-BCFF-E0F180BC7805}"/>
+    <hyperlink ref="E12" r:id="rId72" xr:uid="{9BAD52EC-0FBB-47D0-B299-98976A4A44C1}"/>
+    <hyperlink ref="E13" r:id="rId73" xr:uid="{BBB29648-EE03-4690-B8CF-7336712FAED6}"/>
+    <hyperlink ref="E3" r:id="rId74" xr:uid="{02DC2D59-84BF-4EEB-AE0B-79A2F174ED4E}"/>
+    <hyperlink ref="E39" r:id="rId75" xr:uid="{A63C04C4-8DD9-435D-ABF9-0203E47DF1B0}"/>
+    <hyperlink ref="E40" r:id="rId76" xr:uid="{8E647A81-A99D-4893-8BBE-EA2D0B10E098}"/>
+    <hyperlink ref="E14" r:id="rId77" xr:uid="{2E33A0D8-379C-435E-914F-1511B519A04E}"/>
+    <hyperlink ref="E4" r:id="rId78" xr:uid="{28D87A6B-7FF4-40B3-B258-618F4D30BC9B}"/>
+    <hyperlink ref="E16" r:id="rId79" xr:uid="{EB604F45-7F62-4D95-87A0-7C607F70EEE6}"/>
+    <hyperlink ref="E42" r:id="rId80" xr:uid="{FF0F238A-0D26-48C4-A15F-7954889B76EF}"/>
+    <hyperlink ref="E44" r:id="rId81" xr:uid="{6A9F5AC2-0769-4F65-A1B3-C7B6B78865CF}"/>
+    <hyperlink ref="E17" r:id="rId82" xr:uid="{8F8CC71E-CB4F-469E-8417-A15A6E522D48}"/>
+    <hyperlink ref="E45" r:id="rId83" xr:uid="{70588B6D-86C2-4E9D-A653-EB43F4458978}"/>
+    <hyperlink ref="E18" r:id="rId84" xr:uid="{2BC13BFC-19BE-477A-82E0-7D14CED900F5}"/>
+    <hyperlink ref="E46" r:id="rId85" xr:uid="{7A331BB3-C033-4479-BE55-986C3D9F9A53}"/>
+    <hyperlink ref="E47" r:id="rId86" xr:uid="{9D770BB2-4EC1-4C1B-9178-82ADFA28631B}"/>
+    <hyperlink ref="E7" r:id="rId87" xr:uid="{9BCD1D34-3807-4EFF-9AFB-1B2D272BAC40}"/>
+    <hyperlink ref="E48" r:id="rId88" xr:uid="{D7E4C853-E250-43E6-9D4D-F09FCBFF6B2F}"/>
+    <hyperlink ref="E49" r:id="rId89" xr:uid="{74D7670D-4811-4714-AC93-1B08F70715DA}"/>
+    <hyperlink ref="E19" r:id="rId90" xr:uid="{CB748B89-0123-4681-825A-E27A0BE8ECB1}"/>
+    <hyperlink ref="E51" r:id="rId91" xr:uid="{4D3EFA2A-19FF-4AD8-84E1-C8E13C595478}"/>
+    <hyperlink ref="E53" r:id="rId92" xr:uid="{A4C956F3-167F-4BD7-A91C-26AD208A0BD1}"/>
+    <hyperlink ref="E54" r:id="rId93" xr:uid="{1749D594-EE49-4E34-B8D1-987FAE0B65C9}"/>
+    <hyperlink ref="E56" r:id="rId94" xr:uid="{1380FF99-EF25-4839-8AF5-637A67A7D467}"/>
+    <hyperlink ref="E57" r:id="rId95" xr:uid="{4E15A300-DD30-44C2-BA8F-B49EEC02963B}"/>
+    <hyperlink ref="E58" r:id="rId96" xr:uid="{0F99CB0B-4B4B-4B69-9AC3-D56535324B5D}"/>
+    <hyperlink ref="E20" r:id="rId97" xr:uid="{D941B546-8A6E-4F9C-AEA8-DF3FB2FD1934}"/>
+    <hyperlink ref="E21" r:id="rId98" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
+    <hyperlink ref="E22" r:id="rId99" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
+    <hyperlink ref="F56" r:id="rId100" xr:uid="{435B592D-DD21-4EC5-9AFF-18B7F3BB085D}"/>
+    <hyperlink ref="F22" r:id="rId101" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
+    <hyperlink ref="F21" r:id="rId102" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
+    <hyperlink ref="E15" r:id="rId103" xr:uid="{25D99204-4613-42A1-BE9B-F2E5D561C894}"/>
+    <hyperlink ref="E11" r:id="rId104" xr:uid="{8F612C67-B290-475F-A329-18B4A1CD494F}"/>
+    <hyperlink ref="E41" r:id="rId105" xr:uid="{C9CED6DD-2DA0-41FC-871A-F66D82DD880B}"/>
+    <hyperlink ref="E43" r:id="rId106" xr:uid="{60B932FB-29EC-45F2-B889-1CB79A7CA2CB}"/>
+    <hyperlink ref="E50" r:id="rId107" xr:uid="{A29855BD-159B-419E-AEF2-13C042924D47}"/>
+    <hyperlink ref="E33" r:id="rId108" xr:uid="{8075B8C8-FB88-7B49-BD90-E19F35481EB2}"/>
+    <hyperlink ref="E52" r:id="rId109" xr:uid="{D13B153E-E756-3347-A1AB-AB3EE4BA2858}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId108"/>
+    <tablePart r:id="rId110"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -7109,7 +7090,7 @@
       <c r="A25" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="24" t="s">
         <v>453</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -7169,7 +7150,7 @@
       <c r="A26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="24" t="s">
         <v>454</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -7226,7 +7207,7 @@
       <c r="A27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="24" t="s">
         <v>455</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -7283,7 +7264,7 @@
       <c r="A28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="24" t="s">
         <v>456</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -7337,7 +7318,7 @@
       <c r="A29" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="24" t="s">
         <v>457</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -7391,7 +7372,7 @@
       <c r="A30" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="24" t="s">
         <v>458</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -7448,7 +7429,7 @@
       <c r="A31" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="24" t="s">
         <v>459</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -7506,7 +7487,7 @@
       <c r="A32" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="24" t="s">
         <v>460</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -7563,7 +7544,7 @@
       <c r="A33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="24" t="s">
         <v>461</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -7620,7 +7601,7 @@
       <c r="A34" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="24" t="s">
         <v>462</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -7680,7 +7661,7 @@
       <c r="A35" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="24" t="s">
         <v>463</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -7734,7 +7715,7 @@
       <c r="A36" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="24" t="s">
         <v>464</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -7791,7 +7772,7 @@
       <c r="A37" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="24" t="s">
         <v>465</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -7848,7 +7829,7 @@
       <c r="A38" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="24" t="s">
         <v>466</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -7898,7 +7879,7 @@
       <c r="A39" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="24" t="s">
         <v>467</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -7955,7 +7936,7 @@
       <c r="A40" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="24" t="s">
         <v>468</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -8009,7 +7990,7 @@
       <c r="A41" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="24" t="s">
         <v>469</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -8067,7 +8048,7 @@
       <c r="A42" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="24" t="s">
         <v>470</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -8124,7 +8105,7 @@
       <c r="A43" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="24" t="s">
         <v>471</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -8174,7 +8155,7 @@
       <c r="A44" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="24" t="s">
         <v>472</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -8222,7 +8203,7 @@
       <c r="A45" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="24" t="s">
         <v>473</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -8273,7 +8254,7 @@
       <c r="A46" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="24" t="s">
         <v>474</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -8330,7 +8311,7 @@
       <c r="A47" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="24" t="s">
         <v>475</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -8390,7 +8371,7 @@
       <c r="A48" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="24" t="s">
         <v>476</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -8447,7 +8428,7 @@
       <c r="A49" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="24" t="s">
         <v>477</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -8496,7 +8477,7 @@
       <c r="A50" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="24" t="s">
         <v>478</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -8551,7 +8532,7 @@
       <c r="A51" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="24" t="s">
         <v>479</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -8604,7 +8585,7 @@
       <c r="A52" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="24" t="s">
         <v>480</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -8661,7 +8642,7 @@
       <c r="A53" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="24" t="s">
         <v>481</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -8720,7 +8701,7 @@
       <c r="A54" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="24" t="s">
         <v>482</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -8777,7 +8758,7 @@
       <c r="A55" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="24" t="s">
         <v>69</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -8834,7 +8815,7 @@
       <c r="A56" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="24" t="s">
         <v>483</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -8888,7 +8869,7 @@
       <c r="A57" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="24" t="s">
         <v>484</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -8947,7 +8928,7 @@
       <c r="A58" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="24" t="s">
         <v>485</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -9003,15 +8984,15 @@
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A59" s="26"/>
-      <c r="B59" s="29" t="s">
+      <c r="A59" s="21"/>
+      <c r="B59" s="24" t="s">
         <v>486</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="27"/>
+      <c r="E59" s="22"/>
       <c r="F59" s="7"/>
-      <c r="G59" s="28"/>
+      <c r="G59" s="23"/>
       <c r="H59" s="1"/>
       <c r="I59"/>
       <c r="O59" s="4"/>
@@ -9024,19 +9005,19 @@
       <c r="A61" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="B61" s="23"/>
+      <c r="B61" s="14"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="B62" s="24"/>
+      <c r="B62" s="15"/>
     </row>
     <row r="63" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="B63" s="25"/>
+      <c r="B63" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="12">
@@ -9236,32 +9217,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ArtifactsRequested_x003f_ xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">Yes</ArtifactsRequested_x003f_>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6f04fd38-88d0-493d-bcfe-f0680152bc54" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010067084DD94AAF9F49A29187A8281A736B" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31370f96594e886cf5a1a287283c7112">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e" xmlns:ns3="9843afbf-a983-44da-9ef0-770fe2475dd9" xmlns:ns4="6f04fd38-88d0-493d-bcfe-f0680152bc54" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd273aee41ba6857014841f4b535fddc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
@@ -9535,34 +9490,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E5FD91-6CDF-4778-8B48-65EB30B9BE76}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
-    <ds:schemaRef ds:uri="6f04fd38-88d0-493d-bcfe-f0680152bc54"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ArtifactsRequested_x003f_ xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">Yes</ArtifactsRequested_x003f_>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6f04fd38-88d0-493d-bcfe-f0680152bc54" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08ABF4CA-0893-4703-B384-163F0489B58B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9580,4 +9534,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E5FD91-6CDF-4778-8B48-65EB30B9BE76}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
+    <ds:schemaRef ds:uri="6f04fd38-88d0-493d-bcfe-f0680152bc54"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/updatedMemberData.xlsx
+++ b/updatedMemberData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madmarshall/Documents/medicaidOversightMap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB0BD0E-7263-EC42-BB7D-4AA520EB14B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65A340F-9EFD-5849-88C1-447E468EF906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7100" yWindow="660" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="960" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="495">
   <si>
     <t>Oversight?</t>
   </si>
@@ -1516,10 +1516,13 @@
     <t>https://dph.georgia.gov/about-dph</t>
   </si>
   <si>
-    <t>https://www.chfs.ky.gov/agencies/Pages/default.aspx</t>
-  </si>
-  <si>
     <t>https://www.tn.gov/health/dept.html</t>
+  </si>
+  <si>
+    <t>Kentucky Cabinet for Health and Family Services</t>
+  </si>
+  <si>
+    <t>https://www.chfs.ky.gov/services/Pages/search.aspx</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1866,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U58" totalsRowShown="0">
   <autoFilter ref="A1:U58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U58">
-    <sortCondition descending="1" ref="A1:A58"/>
+    <sortCondition ref="B1:B58"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="24" xr3:uid="{EC3A8AE4-1AEA-44FE-9DAE-C845A25235D5}" name="Oversight?" dataDxfId="13"/>
@@ -2329,111 +2332,105 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>450</v>
+      <c r="A2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>430</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>492</v>
+        <v>23</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="1" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>312</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>314</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>315</v>
+        <v>28</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>316</v>
+        <v>29</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="3">
-        <v>4588372</v>
+        <v>5157699</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="T2" t="s">
         <v>32</v>
       </c>
       <c r="U2" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>453</v>
+        <v>288</v>
+      </c>
+      <c r="B3" t="s">
+        <v>431</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>335</v>
+        <v>268</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>336</v>
+      <c r="E3" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>337</v>
+        <v>270</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>339</v>
+        <v>272</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>340</v>
+        <v>273</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>341</v>
+        <v>274</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>336</v>
+        <v>269</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="Q3" s="3">
-        <v>10140459</v>
+        <v>740133</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>90</v>
@@ -2442,162 +2439,169 @@
         <v>41</v>
       </c>
       <c r="T3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>458</v>
+      <c r="A4" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>432</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>348</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>349</v>
+        <v>234</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="I4"/>
       <c r="J4" s="1" t="s">
-        <v>351</v>
+        <v>237</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>352</v>
+        <v>238</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>353</v>
+        <v>239</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>349</v>
+        <v>235</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>2005465</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="Q4" s="3"/>
       <c r="R4" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S4" t="s">
         <v>41</v>
       </c>
       <c r="T4" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="U4" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>443</v>
+      <c r="A5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>433</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>289</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I5"/>
-      <c r="J5" s="1" t="s">
-        <v>292</v>
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>293</v>
+        <v>39</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>294</v>
+        <v>40</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q5" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>7582384</v>
+      </c>
       <c r="R5" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S5" t="s">
         <v>41</v>
       </c>
       <c r="T5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U5" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>449</v>
+      <c r="A6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>434</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>306</v>
+        <v>48</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>307</v>
+        <v>50</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>308</v>
+        <v>51</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>304</v>
+        <v>44</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="3">
-        <v>2970606</v>
+        <v>3088354</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>30</v>
@@ -2613,118 +2617,111 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>469</v>
+      <c r="A7" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" t="s">
+        <v>435</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="I7" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>387</v>
+        <v>279</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>388</v>
+        <v>280</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>389</v>
+        <v>276</v>
       </c>
       <c r="Q7" s="3">
-        <v>4272371</v>
-      </c>
-      <c r="R7" s="1"/>
+        <v>39431263</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="S7" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T7" t="s">
-        <v>219</v>
+        <v>42</v>
       </c>
       <c r="U7" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>258</v>
+      <c r="A8" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>268</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>269</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>270</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>272</v>
+        <v>55</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>273</v>
+        <v>56</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>274</v>
+        <v>57</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>269</v>
+        <v>53</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>271</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="3">
-        <v>740133</v>
+        <v>5957493</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S8" t="s">
         <v>41</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U8" t="s">
         <v>41</v>
@@ -2734,111 +2731,107 @@
       <c r="A9" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B9" t="s">
-        <v>435</v>
+      <c r="B9" s="24" t="s">
+        <v>466</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>275</v>
+        <v>376</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="I9"/>
       <c r="J9" s="1" t="s">
-        <v>278</v>
+        <v>379</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>279</v>
+        <v>380</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>280</v>
+        <v>381</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>39431263</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="Q9" s="3"/>
       <c r="R9" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S9" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="T9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U9" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>438</v>
+      <c r="A10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>437</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>283</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>284</v>
+        <v>61</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>285</v>
+        <v>62</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>286</v>
+        <v>63</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="Q10" s="3">
-        <v>1051917</v>
+        <v>3675069</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U10" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -2846,212 +2839,211 @@
         <v>258</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="Q11" s="3">
-        <v>2001619</v>
+        <v>1051917</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S11" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="T11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U11" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
-        <v>258</v>
+      <c r="A12" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>321</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>322</v>
+        <v>67</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>323</v>
+        <v>68</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>324</v>
+        <v>69</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>325</v>
+        <v>65</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>326</v>
+        <v>70</v>
       </c>
       <c r="Q12" s="3">
-        <v>1405012</v>
+        <v>702250</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S12" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="T12" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="U12" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
-        <v>258</v>
+      <c r="A13" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>327</v>
+        <v>240</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="1" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="I13" t="s">
-        <v>37</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="I13"/>
       <c r="J13" s="1" t="s">
-        <v>330</v>
+        <v>243</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>332</v>
+        <v>245</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>7136171</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Q13" s="3"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S13" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="T13" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="U13" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>457</v>
+      <c r="A14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>342</v>
+        <v>72</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>343</v>
+        <v>73</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>345</v>
+        <v>76</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>343</v>
+        <v>73</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>347</v>
+        <v>76</v>
       </c>
       <c r="Q14" s="3">
-        <v>1137233</v>
+        <v>23372215</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>30</v>
@@ -3067,270 +3059,266 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>459</v>
+      <c r="A15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F15" s="7"/>
+        <v>491</v>
+      </c>
+      <c r="F15" s="8"/>
       <c r="G15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="I15"/>
+        <v>80</v>
+      </c>
+      <c r="I15" t="s">
+        <v>75</v>
+      </c>
       <c r="J15" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>355</v>
+        <v>83</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="3">
-        <v>3267467</v>
+        <v>11180878</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S15" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T15" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="U15" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>460</v>
+      <c r="A16" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>362</v>
+        <v>289</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="I16"/>
       <c r="J16" s="1" t="s">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>366</v>
+        <v>293</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1409032</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="Q16" s="3"/>
       <c r="R16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S16" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="U16" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>464</v>
+      <c r="A17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>371</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>373</v>
+        <v>87</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>374</v>
+        <v>88</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>375</v>
+        <v>89</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>370</v>
+        <v>85</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="Q17" s="3">
-        <v>11046024</v>
+        <v>1446146</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S17" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U17" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>466</v>
+      <c r="B18" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>377</v>
+        <v>296</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="I18"/>
+        <v>297</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
       <c r="J18" s="1" t="s">
-        <v>379</v>
+        <v>298</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>380</v>
+        <v>299</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q18" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>2001619</v>
+      </c>
       <c r="R18" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S18" t="s">
+        <v>71</v>
+      </c>
+      <c r="T18" t="s">
         <v>31</v>
       </c>
-      <c r="T18" t="s">
-        <v>41</v>
-      </c>
       <c r="U18" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>474</v>
+      <c r="A19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>404</v>
+        <v>91</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>405</v>
+        <v>92</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>406</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>407</v>
+        <v>94</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>408</v>
+        <v>95</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>409</v>
+        <v>96</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>405</v>
+        <v>92</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>410</v>
+        <v>97</v>
       </c>
       <c r="Q19" s="3">
-        <v>1112308</v>
+        <v>12710158</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>30</v>
@@ -3342,432 +3330,457 @@
         <v>42</v>
       </c>
       <c r="U19" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>483</v>
+      <c r="A20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>411</v>
+        <v>98</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>412</v>
+        <v>99</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="I20" t="s">
         <v>37</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>414</v>
+      <c r="J20" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>415</v>
+        <v>103</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>416</v>
+        <v>104</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>412</v>
+        <v>99</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="Q20" s="3">
-        <v>1792147</v>
+        <v>6924275</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S20" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T20" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="U20" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>484</v>
+      <c r="A21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>260</v>
+        <v>105</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>262</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F21" s="7"/>
       <c r="G21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>263</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
         <v>37</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>264</v>
+        <v>108</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>261</v>
+        <v>106</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>267</v>
+        <v>112</v>
       </c>
       <c r="Q21" s="3">
-        <v>5822434</v>
+        <v>3241488</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S21" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="T21" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U21" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>485</v>
+      <c r="A22" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D22" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>419</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F22" s="7"/>
       <c r="G22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>420</v>
+        <v>305</v>
       </c>
       <c r="I22" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>422</v>
+        <v>306</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>418</v>
+        <v>304</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="Q22" s="3">
-        <v>578759</v>
+        <v>2970606</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S22" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="T22" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U22" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>472</v>
+      <c r="A23" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>391</v>
+        <v>493</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F23" s="7"/>
       <c r="G23" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="I23"/>
+        <v>312</v>
+      </c>
+      <c r="I23" t="s">
+        <v>75</v>
+      </c>
       <c r="J23" s="1" t="s">
-        <v>393</v>
+        <v>313</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>394</v>
+        <v>314</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>395</v>
+        <v>315</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q23" s="3"/>
+        <v>316</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>4588372</v>
+      </c>
       <c r="R23" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S23" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="T23" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="U23" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>473</v>
+      <c r="A24" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>451</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="8"/>
+      <c r="E24" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F24" s="7"/>
       <c r="G24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1405012</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S24" t="s">
+        <v>219</v>
+      </c>
+      <c r="T24" t="s">
+        <v>219</v>
+      </c>
+      <c r="U24" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I24"/>
-      <c r="J24" s="1" t="s">
+      <c r="I25"/>
+      <c r="J25" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="1" t="s">
+      <c r="Q25" s="3"/>
+      <c r="R25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S24" t="s">
+      <c r="S25" t="s">
         <v>71</v>
       </c>
-      <c r="T24" t="s">
+      <c r="T25" t="s">
         <v>42</v>
       </c>
-      <c r="U24" t="s">
+      <c r="U25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
-        <v>430</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>5157699</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S25" t="s">
-        <v>31</v>
-      </c>
-      <c r="T25" t="s">
-        <v>32</v>
-      </c>
-      <c r="U25" t="s">
-        <v>31</v>
-      </c>
-    </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>432</v>
+      <c r="A26" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>233</v>
+        <v>327</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>235</v>
+        <v>328</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="I26"/>
+        <v>329</v>
+      </c>
+      <c r="I26" t="s">
+        <v>37</v>
+      </c>
       <c r="J26" s="1" t="s">
-        <v>237</v>
+        <v>330</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>238</v>
+        <v>331</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>239</v>
+        <v>332</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q26" s="3"/>
+        <v>334</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>7136171</v>
+      </c>
       <c r="R26" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S26" t="s">
         <v>41</v>
       </c>
       <c r="T26" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="U26" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>433</v>
+      <c r="A27" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>453</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>335</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="F27" s="7"/>
       <c r="G27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>36</v>
+        <v>337</v>
       </c>
       <c r="I27" t="s">
         <v>37</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>38</v>
+      <c r="J27" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>34</v>
+        <v>336</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="Q27" s="3">
-        <v>7582384</v>
+        <v>10140459</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S27" t="s">
         <v>41</v>
@@ -3783,50 +3796,45 @@
       <c r="A28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B28" t="s">
-        <v>434</v>
+      <c r="B28" s="24" t="s">
+        <v>454</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>45</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F28" s="7"/>
       <c r="G28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="I28" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="3">
-        <v>3088354</v>
+        <v>5793151</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>30</v>
@@ -3845,102 +3853,99 @@
       <c r="A29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B29" t="s">
-        <v>436</v>
+      <c r="B29" s="24" t="s">
+        <v>455</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="1" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="Q29" s="3">
-        <v>5957493</v>
+        <v>2943045</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S29" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="T29" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U29" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B30" t="s">
-        <v>437</v>
+      <c r="B30" s="24" t="s">
+        <v>456</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>59</v>
+        <v>488</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="I30" t="s">
         <v>37</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="Q30" s="3">
-        <v>3675069</v>
+        <v>6245466</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>30</v>
@@ -3956,105 +3961,102 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>439</v>
+      <c r="A31" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>457</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>342</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>65</v>
+        <v>343</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>66</v>
+        <v>344</v>
       </c>
       <c r="I31" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>68</v>
+        <v>345</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>69</v>
+        <v>346</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>65</v>
+        <v>343</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>70</v>
+        <v>347</v>
       </c>
       <c r="Q31" s="3">
-        <v>702250</v>
+        <v>1137233</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S31" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="T31" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="U31" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>440</v>
+      <c r="A32" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>458</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>72</v>
+        <v>348</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>73</v>
+        <v>260</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>349</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>74</v>
+        <v>350</v>
       </c>
       <c r="I32" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>73</v>
+        <v>349</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="Q32" s="3">
-        <v>23372215</v>
+        <v>2005465</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -4066,162 +4068,170 @@
         <v>42</v>
       </c>
       <c r="U32" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>441</v>
+      <c r="A33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>459</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F33" s="8"/>
+        <v>487</v>
+      </c>
+      <c r="F33" s="7"/>
       <c r="G33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I33" t="s">
-        <v>75</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="I33"/>
       <c r="J33" s="1" t="s">
-        <v>81</v>
+        <v>357</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>83</v>
+        <v>360</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="Q33" s="3">
-        <v>11180878</v>
+        <v>3267467</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S33" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="T33" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="U33" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>442</v>
+      <c r="A34" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>460</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>240</v>
+        <v>362</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>241</v>
+        <v>363</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="1" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I34"/>
+        <v>364</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
       <c r="J34" s="1" t="s">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>244</v>
+        <v>366</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>245</v>
+        <v>367</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>241</v>
+        <v>363</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q34" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1409032</v>
+      </c>
       <c r="R34" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S34" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="T34" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="U34" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>444</v>
+      <c r="B35" s="24" t="s">
+        <v>461</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="1" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="I35" t="s">
-        <v>47</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="3">
-        <v>1446146</v>
+        <v>9500851</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S35" t="s">
         <v>41</v>
@@ -4237,45 +4247,48 @@
       <c r="A36" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>446</v>
+      <c r="B36" s="24" t="s">
+        <v>462</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>92</v>
+        <v>489</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="I36" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>94</v>
+        <v>142</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="3">
-        <v>12710158</v>
+        <v>2130256</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>30</v>
@@ -4294,117 +4307,111 @@
       <c r="A37" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>447</v>
+      <c r="B37" s="24" t="s">
+        <v>463</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="I37" t="s">
         <v>37</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="3">
-        <v>6924275</v>
+        <v>19867248</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S37" t="s">
         <v>41</v>
       </c>
       <c r="T37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U37" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>448</v>
+      <c r="A38" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>464</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>105</v>
+        <v>369</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>106</v>
+        <v>370</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>107</v>
+        <v>371</v>
       </c>
       <c r="I38" t="s">
         <v>37</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>110</v>
+        <v>374</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>111</v>
+        <v>375</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>112</v>
+        <v>370</v>
       </c>
       <c r="Q38" s="3">
-        <v>3241488</v>
+        <v>11046024</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S38" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="T38" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U38" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
@@ -4412,44 +4419,44 @@
         <v>20</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="I39" t="s">
         <v>37</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="Q39" s="3">
-        <v>5793151</v>
+        <v>796568</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>30</v>
@@ -4458,7 +4465,7 @@
         <v>41</v>
       </c>
       <c r="T39" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U39" t="s">
         <v>41</v>
@@ -4469,56 +4476,56 @@
         <v>20</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="1" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="I40" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="Q40" s="3">
-        <v>2943045</v>
+        <v>11883304</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S40" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U40" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
@@ -4526,41 +4533,41 @@
         <v>20</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>488</v>
+        <v>166</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="I41" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="Q41" s="3">
-        <v>6245466</v>
+        <v>4095393</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>30</v>
@@ -4576,60 +4583,61 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
-        <v>20</v>
+      <c r="A42" s="14" t="s">
+        <v>288</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>132</v>
+        <v>382</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>133</v>
+        <v>383</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="1" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>135</v>
+        <v>384</v>
       </c>
       <c r="I42" t="s">
         <v>37</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>136</v>
+      <c r="J42" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>137</v>
+        <v>387</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>138</v>
+        <v>388</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>133</v>
+        <v>383</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="Q42" s="3">
-        <v>9500851</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>4272371</v>
+      </c>
+      <c r="R42" s="1"/>
       <c r="S42" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="T42" t="s">
-        <v>42</v>
+        <v>219</v>
       </c>
       <c r="U42" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
@@ -4637,47 +4645,44 @@
         <v>20</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>489</v>
+        <v>173</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="Q43" s="3">
-        <v>2130256</v>
+        <v>13078751</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>30</v>
@@ -4697,155 +4702,142 @@
         <v>20</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>147</v>
+        <v>247</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44" t="s">
-        <v>37</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I44"/>
       <c r="J44" s="1" t="s">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>19867248</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="Q44" s="3"/>
       <c r="R44" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S44" t="s">
         <v>41</v>
       </c>
       <c r="T44" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="U44" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45" s="13" t="s">
-        <v>20</v>
+      <c r="A45" s="17" t="s">
+        <v>390</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>152</v>
+        <v>391</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="7"/>
+        <v>260</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I45" t="s">
-        <v>37</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="I45"/>
       <c r="J45" s="1" t="s">
-        <v>155</v>
+        <v>393</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>156</v>
+        <v>395</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>796568</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="Q45" s="3"/>
       <c r="R45" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S45" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="T45" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="U45" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" s="13" t="s">
-        <v>20</v>
+      <c r="A46" s="15" t="s">
+        <v>403</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>159</v>
+        <v>404</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>161</v>
+        <v>406</v>
       </c>
       <c r="I46" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>162</v>
+        <v>407</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>163</v>
+        <v>408</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>164</v>
+        <v>409</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="Q46" s="3">
-        <v>11883304</v>
+        <v>1112308</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>30</v>
@@ -4854,10 +4846,10 @@
         <v>41</v>
       </c>
       <c r="T46" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U46" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
@@ -4865,53 +4857,59 @@
         <v>20</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>166</v>
+        <v>490</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="I47" t="s">
-        <v>168</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>169</v>
+        <v>47</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>166</v>
+        <v>179</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="Q47" s="3">
-        <v>4095393</v>
+        <v>5478831</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S47" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="T47" t="s">
         <v>42</v>
       </c>
       <c r="U47" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
@@ -4919,47 +4917,47 @@
         <v>20</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I48" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="Q48" s="3">
-        <v>13078751</v>
+        <v>924669</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S48" t="s">
         <v>41</v>
@@ -4976,38 +4974,39 @@
         <v>20</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>234</v>
+        <v>22</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F49" s="7"/>
+        <v>492</v>
+      </c>
+      <c r="F49" s="8"/>
       <c r="G49" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I49"/>
+        <v>192</v>
+      </c>
+      <c r="I49" t="s">
+        <v>168</v>
+      </c>
       <c r="J49" s="1" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q49" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>7227750</v>
+      </c>
       <c r="R49" s="1" t="s">
         <v>90</v>
       </c>
@@ -5015,7 +5014,7 @@
         <v>41</v>
       </c>
       <c r="T49" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="U49" t="s">
         <v>41</v>
@@ -5026,59 +5025,54 @@
         <v>20</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>490</v>
+        <v>197</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I50" t="s">
-        <v>47</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
+      </c>
+      <c r="I50"/>
+      <c r="J50" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="Q50" s="3">
-        <v>5478831</v>
+        <v>31290831</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>90</v>
       </c>
       <c r="S50" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="T50" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U50" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
@@ -5086,45 +5080,41 @@
         <v>20</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I51" t="s">
-        <v>26</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="I51"/>
       <c r="J51" s="1" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>924669</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="Q51" s="3"/>
       <c r="R51" s="1" t="s">
         <v>90</v>
       </c>
@@ -5132,7 +5122,7 @@
         <v>41</v>
       </c>
       <c r="T51" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="U51" t="s">
         <v>41</v>
@@ -5143,47 +5133,53 @@
         <v>20</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D52" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="F52" s="8"/>
+        <v>205</v>
+      </c>
+      <c r="F52" s="7"/>
       <c r="G52" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="I52" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="Q52" s="3">
-        <v>7227750</v>
+        <v>3503613</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S52" t="s">
         <v>41</v>
       </c>
       <c r="T52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U52" t="s">
         <v>41</v>
@@ -5194,54 +5190,58 @@
         <v>20</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F53" s="7"/>
+        <v>212</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="G53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I53"/>
+        <v>214</v>
+      </c>
+      <c r="I53" t="s">
+        <v>47</v>
+      </c>
       <c r="J53" s="1" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="Q53" s="3">
-        <v>31290831</v>
+        <v>648493</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S53" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="T53" t="s">
         <v>32</v>
       </c>
       <c r="U53" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
@@ -5249,41 +5249,45 @@
         <v>20</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>234</v>
+        <v>22</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="1" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="I54"/>
+        <v>222</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
       <c r="J54" s="1" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q54" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>8535519</v>
+      </c>
       <c r="R54" s="1" t="s">
         <v>90</v>
       </c>
@@ -5291,10 +5295,10 @@
         <v>41</v>
       </c>
       <c r="T54" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="U54" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
@@ -5302,44 +5306,44 @@
         <v>20</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>480</v>
+        <v>69</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D55" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="I55" t="s">
         <v>37</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="Q55" s="3">
-        <v>3503613</v>
+        <v>7614893</v>
       </c>
       <c r="R55" s="1" t="s">
         <v>30</v>
@@ -5355,176 +5359,175 @@
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A56" s="13" t="s">
-        <v>20</v>
+      <c r="A56" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>22</v>
+        <v>411</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>213</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="F56" s="7"/>
       <c r="G56" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>214</v>
+        <v>413</v>
       </c>
       <c r="I56" t="s">
-        <v>47</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>215</v>
+        <v>37</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>217</v>
+        <v>416</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>218</v>
+        <v>412</v>
       </c>
       <c r="Q56" s="3">
-        <v>648493</v>
+        <v>1792147</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S56" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="T56" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="U56" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A57" s="13" t="s">
-        <v>20</v>
+      <c r="A57" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>22</v>
+        <v>259</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>260</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F57" s="7"/>
+        <v>261</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="G57" s="1" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="I57" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="Q57" s="3">
-        <v>8535519</v>
+        <v>5822434</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S57" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="T57" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U57" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>20</v>
+      <c r="A58" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>69</v>
+        <v>485</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>417</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>260</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F58" s="7"/>
+        <v>418</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="G58" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>229</v>
+        <v>420</v>
       </c>
       <c r="I58" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>231</v>
+        <v>421</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>228</v>
+        <v>418</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>230</v>
+        <v>424</v>
       </c>
       <c r="Q58" s="3">
-        <v>7614893</v>
+        <v>578759</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="S58" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="T58" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U58" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
@@ -5568,119 +5571,117 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="O25" r:id="rId1" xr:uid="{079F8495-F7EA-4560-840A-C6CF792DF3BB}"/>
-    <hyperlink ref="O8" r:id="rId2" xr:uid="{CCF9746C-2CEA-4FD1-8FB6-1D7AC38B1637}"/>
-    <hyperlink ref="O26" r:id="rId3" xr:uid="{81A043F0-7269-4E9F-966B-970558EDF915}"/>
-    <hyperlink ref="O27" r:id="rId4" location="org-chart" xr:uid="{B10A13A8-BEAA-492E-A9E1-886989578D2E}"/>
-    <hyperlink ref="O28" r:id="rId5" xr:uid="{C9712B49-7E42-4BAC-B2CC-9396CE557732}"/>
-    <hyperlink ref="O9" r:id="rId6" xr:uid="{31C77042-2672-41FF-B03A-F7069C4C791C}"/>
-    <hyperlink ref="O29" r:id="rId7" xr:uid="{284B56AD-5393-43F6-8EA1-2476F738B5BD}"/>
-    <hyperlink ref="O30" r:id="rId8" xr:uid="{6F86E295-4976-43B3-AEB6-F5603F753AA1}"/>
-    <hyperlink ref="O10" r:id="rId9" xr:uid="{8228381B-7C0B-475D-9331-F94F0978FE2E}"/>
-    <hyperlink ref="O31" r:id="rId10" xr:uid="{9DC2CC16-C79F-4DBE-B060-E56DEF888135}"/>
-    <hyperlink ref="O32" r:id="rId11" xr:uid="{CCB8BF42-4383-4F43-9AC1-361BCED8CF91}"/>
-    <hyperlink ref="O34" r:id="rId12" xr:uid="{C2D68443-F05F-4555-A93A-935B47459BEC}"/>
-    <hyperlink ref="O5" r:id="rId13" xr:uid="{5978066A-6949-4053-A2BC-55251F30BEF1}"/>
-    <hyperlink ref="O35" r:id="rId14" xr:uid="{27D74848-FDF5-4E01-82FF-D803BA7573A4}"/>
-    <hyperlink ref="O11" r:id="rId15" xr:uid="{99A6B5C4-2CBD-423F-8602-BF8D7DAF0B12}"/>
-    <hyperlink ref="O36" r:id="rId16" xr:uid="{90A8F58D-AD52-45C8-9C75-013C6F72E669}"/>
-    <hyperlink ref="O37" r:id="rId17" xr:uid="{0A2FA18A-514A-4366-A4EC-51C1EECDD28E}"/>
-    <hyperlink ref="O38" r:id="rId18" xr:uid="{E07E0A34-F6A5-4745-AEEF-3E1D7D81F532}"/>
-    <hyperlink ref="O6" r:id="rId19" xr:uid="{6681FC06-699D-4557-A261-080A7381AFE8}"/>
-    <hyperlink ref="O2" r:id="rId20" xr:uid="{2619FDDF-555F-42A3-87B5-8A609128F3C8}"/>
-    <hyperlink ref="O12" r:id="rId21" xr:uid="{94341740-42F6-49C7-AAFE-AF32E4009868}"/>
-    <hyperlink ref="O13" r:id="rId22" xr:uid="{4B87F942-D74D-4166-970E-F5E5748AC8FB}"/>
-    <hyperlink ref="O3" r:id="rId23" xr:uid="{0993A219-6BF1-4317-A442-00036BB4FC92}"/>
-    <hyperlink ref="O39" r:id="rId24" xr:uid="{1CD243D6-2B7E-4943-B0B2-9FF6A7F4DAD6}"/>
-    <hyperlink ref="O40" r:id="rId25" xr:uid="{41EFFD08-4853-4A26-884E-1DF33B76A091}"/>
-    <hyperlink ref="O41" r:id="rId26" xr:uid="{F467495C-2D06-460C-8031-D4DFC78B4B10}"/>
-    <hyperlink ref="O14" r:id="rId27" xr:uid="{3A81479C-E1E5-40B7-8789-6A2840D4AFC8}"/>
-    <hyperlink ref="O4" r:id="rId28" xr:uid="{1F619310-E327-4DD2-8A71-6E446F73F006}"/>
-    <hyperlink ref="O15" r:id="rId29" xr:uid="{2681B774-ABCC-4F44-B952-8DFDD89DCEBB}"/>
-    <hyperlink ref="O16" r:id="rId30" xr:uid="{FC5E12E2-FD76-4325-8EAD-7C4DDA76A065}"/>
-    <hyperlink ref="O42" r:id="rId31" xr:uid="{7E2A3350-D14F-4A06-951E-30ACE91438AD}"/>
-    <hyperlink ref="O43" r:id="rId32" xr:uid="{83082298-87E6-4F3B-9D14-AB47400E721E}"/>
-    <hyperlink ref="O44" r:id="rId33" xr:uid="{FA22572E-5860-496A-AC81-405711971BED}"/>
-    <hyperlink ref="O17" r:id="rId34" xr:uid="{FF83F8F9-C8A9-4C9A-8CE4-FBCC1BAD81F4}"/>
-    <hyperlink ref="O45" r:id="rId35" xr:uid="{A5D25D1C-155D-44F2-912A-08A4233D68C7}"/>
-    <hyperlink ref="O18" r:id="rId36" xr:uid="{11DB7D3D-A850-4079-A7E0-0E6C2566A9BA}"/>
-    <hyperlink ref="O46" r:id="rId37" xr:uid="{465ED70A-6593-48EC-A551-2C2BF30A4C8D}"/>
-    <hyperlink ref="O47" r:id="rId38" xr:uid="{54894BC2-584D-42CA-B554-32AA68974C32}"/>
-    <hyperlink ref="O7" r:id="rId39" xr:uid="{98E1F1AD-7866-4703-B8AE-A769512E3AB2}"/>
-    <hyperlink ref="O48" r:id="rId40" xr:uid="{D374230A-1E43-4A39-AF8C-EB35DB90FFB3}"/>
-    <hyperlink ref="O49" r:id="rId41" xr:uid="{113308A8-CF5E-4FC5-BE08-A179B8875873}"/>
-    <hyperlink ref="O19" r:id="rId42" xr:uid="{48DB851A-A65D-4C19-9DA6-C08E306672B0}"/>
-    <hyperlink ref="O50" r:id="rId43" xr:uid="{AB47AAE3-F3FC-4F4E-8B96-AFCD45801C87}"/>
-    <hyperlink ref="O51" r:id="rId44" xr:uid="{94D77222-2596-443F-A198-D1ACA09491C2}"/>
-    <hyperlink ref="O53" r:id="rId45" xr:uid="{31F276A7-B8A7-4948-AD8C-2B424176A3F5}"/>
-    <hyperlink ref="O54" r:id="rId46" xr:uid="{3E3BD377-1012-48DD-9D8E-EE9BDAEC6E1C}"/>
-    <hyperlink ref="O56" r:id="rId47" xr:uid="{9EDFD108-00F8-4944-853D-9CF322D9F19C}"/>
-    <hyperlink ref="O57" r:id="rId48" xr:uid="{D7B0DACD-5FD1-4346-B4E7-958EFDE6DA7C}"/>
-    <hyperlink ref="O58" r:id="rId49" xr:uid="{55EB6149-0908-4B53-A043-978695B6AFF2}"/>
-    <hyperlink ref="O20" r:id="rId50" xr:uid="{566E4284-EA29-42AE-ADF0-6D11CA2D7918}"/>
-    <hyperlink ref="O21" r:id="rId51" xr:uid="{1F555AFE-78CF-4F3C-9D4D-8A9484A22E05}"/>
-    <hyperlink ref="O22" r:id="rId52" xr:uid="{A07AD047-9BF8-4A20-B9F9-4A6749EA616A}"/>
-    <hyperlink ref="E25" r:id="rId53" xr:uid="{FEE37E5B-198F-4348-8CCA-D7ED5F656AAC}"/>
-    <hyperlink ref="E8" r:id="rId54" xr:uid="{03D7C8ED-BBB4-45E8-BC5C-86ACD2650E41}"/>
-    <hyperlink ref="E26" r:id="rId55" xr:uid="{0CC618F9-D07B-4A57-BB30-DA9D9C4F2552}"/>
-    <hyperlink ref="E27" r:id="rId56" location="org-chart" xr:uid="{4B9B4038-25F7-4818-A396-E389A8472AC5}"/>
-    <hyperlink ref="E28" r:id="rId57" xr:uid="{A28EE9FF-23D1-4089-A2E1-68FA61B83DF6}"/>
-    <hyperlink ref="E9" r:id="rId58" xr:uid="{EBF8C6EF-5F76-4B85-B16F-3C00DCF81CE8}"/>
-    <hyperlink ref="E29" r:id="rId59" xr:uid="{6E216DFF-697F-4D2E-8F78-1FEF1CEC39BD}"/>
-    <hyperlink ref="E30" r:id="rId60" xr:uid="{736C7E7B-A325-49CD-995B-BEA88AFBE739}"/>
-    <hyperlink ref="E10" r:id="rId61" xr:uid="{7FBF4A86-93BE-4208-85BD-4C057C9D0673}"/>
-    <hyperlink ref="E31" r:id="rId62" xr:uid="{55A76AD9-7045-45D5-9195-B69B42AF0802}"/>
-    <hyperlink ref="E32" r:id="rId63" xr:uid="{029BF59C-D9AF-4315-B2A4-78BE99C97F94}"/>
-    <hyperlink ref="E34" r:id="rId64" xr:uid="{3D68E0F6-565A-4E31-8041-14A4E4AAA026}"/>
-    <hyperlink ref="E5" r:id="rId65" xr:uid="{EF1D420F-18EF-4E76-89A3-98850C9AF20C}"/>
-    <hyperlink ref="E35" r:id="rId66" xr:uid="{F78DA305-9BB5-4F2E-B4F8-66EC8FBDDA3D}"/>
-    <hyperlink ref="E36" r:id="rId67" xr:uid="{34B32381-DA3D-48A1-8F3A-7BA553623903}"/>
-    <hyperlink ref="E37" r:id="rId68" xr:uid="{45465AA5-EEE0-48FC-9065-53047723500D}"/>
-    <hyperlink ref="E38" r:id="rId69" xr:uid="{13BB9942-A405-4DA2-8E06-01F90B4BD748}"/>
-    <hyperlink ref="E6" r:id="rId70" xr:uid="{DA4BEBE2-080E-4CD9-B20D-9A66E0B9BA0E}"/>
-    <hyperlink ref="E2" r:id="rId71" xr:uid="{2A421EFC-5CE1-4915-BCFF-E0F180BC7805}"/>
-    <hyperlink ref="E12" r:id="rId72" xr:uid="{9BAD52EC-0FBB-47D0-B299-98976A4A44C1}"/>
-    <hyperlink ref="E13" r:id="rId73" xr:uid="{BBB29648-EE03-4690-B8CF-7336712FAED6}"/>
-    <hyperlink ref="E3" r:id="rId74" xr:uid="{02DC2D59-84BF-4EEB-AE0B-79A2F174ED4E}"/>
-    <hyperlink ref="E39" r:id="rId75" xr:uid="{A63C04C4-8DD9-435D-ABF9-0203E47DF1B0}"/>
-    <hyperlink ref="E40" r:id="rId76" xr:uid="{8E647A81-A99D-4893-8BBE-EA2D0B10E098}"/>
-    <hyperlink ref="E14" r:id="rId77" xr:uid="{2E33A0D8-379C-435E-914F-1511B519A04E}"/>
-    <hyperlink ref="E4" r:id="rId78" xr:uid="{28D87A6B-7FF4-40B3-B258-618F4D30BC9B}"/>
-    <hyperlink ref="E16" r:id="rId79" xr:uid="{EB604F45-7F62-4D95-87A0-7C607F70EEE6}"/>
-    <hyperlink ref="E42" r:id="rId80" xr:uid="{FF0F238A-0D26-48C4-A15F-7954889B76EF}"/>
-    <hyperlink ref="E44" r:id="rId81" xr:uid="{6A9F5AC2-0769-4F65-A1B3-C7B6B78865CF}"/>
-    <hyperlink ref="E17" r:id="rId82" xr:uid="{8F8CC71E-CB4F-469E-8417-A15A6E522D48}"/>
-    <hyperlink ref="E45" r:id="rId83" xr:uid="{70588B6D-86C2-4E9D-A653-EB43F4458978}"/>
-    <hyperlink ref="E18" r:id="rId84" xr:uid="{2BC13BFC-19BE-477A-82E0-7D14CED900F5}"/>
-    <hyperlink ref="E46" r:id="rId85" xr:uid="{7A331BB3-C033-4479-BE55-986C3D9F9A53}"/>
-    <hyperlink ref="E47" r:id="rId86" xr:uid="{9D770BB2-4EC1-4C1B-9178-82ADFA28631B}"/>
-    <hyperlink ref="E7" r:id="rId87" xr:uid="{9BCD1D34-3807-4EFF-9AFB-1B2D272BAC40}"/>
-    <hyperlink ref="E48" r:id="rId88" xr:uid="{D7E4C853-E250-43E6-9D4D-F09FCBFF6B2F}"/>
-    <hyperlink ref="E49" r:id="rId89" xr:uid="{74D7670D-4811-4714-AC93-1B08F70715DA}"/>
-    <hyperlink ref="E19" r:id="rId90" xr:uid="{CB748B89-0123-4681-825A-E27A0BE8ECB1}"/>
-    <hyperlink ref="E51" r:id="rId91" xr:uid="{4D3EFA2A-19FF-4AD8-84E1-C8E13C595478}"/>
-    <hyperlink ref="E53" r:id="rId92" xr:uid="{A4C956F3-167F-4BD7-A91C-26AD208A0BD1}"/>
-    <hyperlink ref="E54" r:id="rId93" xr:uid="{1749D594-EE49-4E34-B8D1-987FAE0B65C9}"/>
-    <hyperlink ref="E56" r:id="rId94" xr:uid="{1380FF99-EF25-4839-8AF5-637A67A7D467}"/>
-    <hyperlink ref="E57" r:id="rId95" xr:uid="{4E15A300-DD30-44C2-BA8F-B49EEC02963B}"/>
-    <hyperlink ref="E58" r:id="rId96" xr:uid="{0F99CB0B-4B4B-4B69-9AC3-D56535324B5D}"/>
-    <hyperlink ref="E20" r:id="rId97" xr:uid="{D941B546-8A6E-4F9C-AEA8-DF3FB2FD1934}"/>
-    <hyperlink ref="E21" r:id="rId98" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
-    <hyperlink ref="E22" r:id="rId99" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
-    <hyperlink ref="F56" r:id="rId100" xr:uid="{435B592D-DD21-4EC5-9AFF-18B7F3BB085D}"/>
-    <hyperlink ref="F22" r:id="rId101" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
-    <hyperlink ref="F21" r:id="rId102" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
-    <hyperlink ref="E15" r:id="rId103" xr:uid="{25D99204-4613-42A1-BE9B-F2E5D561C894}"/>
-    <hyperlink ref="E11" r:id="rId104" xr:uid="{8F612C67-B290-475F-A329-18B4A1CD494F}"/>
-    <hyperlink ref="E41" r:id="rId105" xr:uid="{C9CED6DD-2DA0-41FC-871A-F66D82DD880B}"/>
-    <hyperlink ref="E43" r:id="rId106" xr:uid="{60B932FB-29EC-45F2-B889-1CB79A7CA2CB}"/>
-    <hyperlink ref="E50" r:id="rId107" xr:uid="{A29855BD-159B-419E-AEF2-13C042924D47}"/>
-    <hyperlink ref="E33" r:id="rId108" xr:uid="{8075B8C8-FB88-7B49-BD90-E19F35481EB2}"/>
-    <hyperlink ref="E52" r:id="rId109" xr:uid="{D13B153E-E756-3347-A1AB-AB3EE4BA2858}"/>
+    <hyperlink ref="O2" r:id="rId1" xr:uid="{079F8495-F7EA-4560-840A-C6CF792DF3BB}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{CCF9746C-2CEA-4FD1-8FB6-1D7AC38B1637}"/>
+    <hyperlink ref="O4" r:id="rId3" xr:uid="{81A043F0-7269-4E9F-966B-970558EDF915}"/>
+    <hyperlink ref="O5" r:id="rId4" location="org-chart" xr:uid="{B10A13A8-BEAA-492E-A9E1-886989578D2E}"/>
+    <hyperlink ref="O6" r:id="rId5" xr:uid="{C9712B49-7E42-4BAC-B2CC-9396CE557732}"/>
+    <hyperlink ref="O7" r:id="rId6" xr:uid="{31C77042-2672-41FF-B03A-F7069C4C791C}"/>
+    <hyperlink ref="O8" r:id="rId7" xr:uid="{284B56AD-5393-43F6-8EA1-2476F738B5BD}"/>
+    <hyperlink ref="O10" r:id="rId8" xr:uid="{6F86E295-4976-43B3-AEB6-F5603F753AA1}"/>
+    <hyperlink ref="O11" r:id="rId9" xr:uid="{8228381B-7C0B-475D-9331-F94F0978FE2E}"/>
+    <hyperlink ref="O12" r:id="rId10" xr:uid="{9DC2CC16-C79F-4DBE-B060-E56DEF888135}"/>
+    <hyperlink ref="O14" r:id="rId11" xr:uid="{CCB8BF42-4383-4F43-9AC1-361BCED8CF91}"/>
+    <hyperlink ref="O13" r:id="rId12" xr:uid="{C2D68443-F05F-4555-A93A-935B47459BEC}"/>
+    <hyperlink ref="O16" r:id="rId13" xr:uid="{5978066A-6949-4053-A2BC-55251F30BEF1}"/>
+    <hyperlink ref="O17" r:id="rId14" xr:uid="{27D74848-FDF5-4E01-82FF-D803BA7573A4}"/>
+    <hyperlink ref="O18" r:id="rId15" xr:uid="{99A6B5C4-2CBD-423F-8602-BF8D7DAF0B12}"/>
+    <hyperlink ref="O19" r:id="rId16" xr:uid="{90A8F58D-AD52-45C8-9C75-013C6F72E669}"/>
+    <hyperlink ref="O20" r:id="rId17" xr:uid="{0A2FA18A-514A-4366-A4EC-51C1EECDD28E}"/>
+    <hyperlink ref="O21" r:id="rId18" xr:uid="{E07E0A34-F6A5-4745-AEEF-3E1D7D81F532}"/>
+    <hyperlink ref="O22" r:id="rId19" xr:uid="{6681FC06-699D-4557-A261-080A7381AFE8}"/>
+    <hyperlink ref="O24" r:id="rId20" xr:uid="{94341740-42F6-49C7-AAFE-AF32E4009868}"/>
+    <hyperlink ref="O26" r:id="rId21" xr:uid="{4B87F942-D74D-4166-970E-F5E5748AC8FB}"/>
+    <hyperlink ref="O27" r:id="rId22" xr:uid="{0993A219-6BF1-4317-A442-00036BB4FC92}"/>
+    <hyperlink ref="O28" r:id="rId23" xr:uid="{1CD243D6-2B7E-4943-B0B2-9FF6A7F4DAD6}"/>
+    <hyperlink ref="O29" r:id="rId24" xr:uid="{41EFFD08-4853-4A26-884E-1DF33B76A091}"/>
+    <hyperlink ref="O30" r:id="rId25" xr:uid="{F467495C-2D06-460C-8031-D4DFC78B4B10}"/>
+    <hyperlink ref="O31" r:id="rId26" xr:uid="{3A81479C-E1E5-40B7-8789-6A2840D4AFC8}"/>
+    <hyperlink ref="O32" r:id="rId27" xr:uid="{1F619310-E327-4DD2-8A71-6E446F73F006}"/>
+    <hyperlink ref="O33" r:id="rId28" xr:uid="{2681B774-ABCC-4F44-B952-8DFDD89DCEBB}"/>
+    <hyperlink ref="O34" r:id="rId29" xr:uid="{FC5E12E2-FD76-4325-8EAD-7C4DDA76A065}"/>
+    <hyperlink ref="O35" r:id="rId30" xr:uid="{7E2A3350-D14F-4A06-951E-30ACE91438AD}"/>
+    <hyperlink ref="O36" r:id="rId31" xr:uid="{83082298-87E6-4F3B-9D14-AB47400E721E}"/>
+    <hyperlink ref="O37" r:id="rId32" xr:uid="{FA22572E-5860-496A-AC81-405711971BED}"/>
+    <hyperlink ref="O38" r:id="rId33" xr:uid="{FF83F8F9-C8A9-4C9A-8CE4-FBCC1BAD81F4}"/>
+    <hyperlink ref="O39" r:id="rId34" xr:uid="{A5D25D1C-155D-44F2-912A-08A4233D68C7}"/>
+    <hyperlink ref="O9" r:id="rId35" xr:uid="{11DB7D3D-A850-4079-A7E0-0E6C2566A9BA}"/>
+    <hyperlink ref="O40" r:id="rId36" xr:uid="{465ED70A-6593-48EC-A551-2C2BF30A4C8D}"/>
+    <hyperlink ref="O41" r:id="rId37" xr:uid="{54894BC2-584D-42CA-B554-32AA68974C32}"/>
+    <hyperlink ref="O42" r:id="rId38" xr:uid="{98E1F1AD-7866-4703-B8AE-A769512E3AB2}"/>
+    <hyperlink ref="O43" r:id="rId39" xr:uid="{D374230A-1E43-4A39-AF8C-EB35DB90FFB3}"/>
+    <hyperlink ref="O44" r:id="rId40" xr:uid="{113308A8-CF5E-4FC5-BE08-A179B8875873}"/>
+    <hyperlink ref="O46" r:id="rId41" xr:uid="{48DB851A-A65D-4C19-9DA6-C08E306672B0}"/>
+    <hyperlink ref="O47" r:id="rId42" xr:uid="{AB47AAE3-F3FC-4F4E-8B96-AFCD45801C87}"/>
+    <hyperlink ref="O48" r:id="rId43" xr:uid="{94D77222-2596-443F-A198-D1ACA09491C2}"/>
+    <hyperlink ref="O50" r:id="rId44" xr:uid="{31F276A7-B8A7-4948-AD8C-2B424176A3F5}"/>
+    <hyperlink ref="O51" r:id="rId45" xr:uid="{3E3BD377-1012-48DD-9D8E-EE9BDAEC6E1C}"/>
+    <hyperlink ref="O53" r:id="rId46" xr:uid="{9EDFD108-00F8-4944-853D-9CF322D9F19C}"/>
+    <hyperlink ref="O54" r:id="rId47" xr:uid="{D7B0DACD-5FD1-4346-B4E7-958EFDE6DA7C}"/>
+    <hyperlink ref="O55" r:id="rId48" xr:uid="{55EB6149-0908-4B53-A043-978695B6AFF2}"/>
+    <hyperlink ref="O56" r:id="rId49" xr:uid="{566E4284-EA29-42AE-ADF0-6D11CA2D7918}"/>
+    <hyperlink ref="O57" r:id="rId50" xr:uid="{1F555AFE-78CF-4F3C-9D4D-8A9484A22E05}"/>
+    <hyperlink ref="O58" r:id="rId51" xr:uid="{A07AD047-9BF8-4A20-B9F9-4A6749EA616A}"/>
+    <hyperlink ref="E2" r:id="rId52" xr:uid="{FEE37E5B-198F-4348-8CCA-D7ED5F656AAC}"/>
+    <hyperlink ref="E3" r:id="rId53" xr:uid="{03D7C8ED-BBB4-45E8-BC5C-86ACD2650E41}"/>
+    <hyperlink ref="E4" r:id="rId54" xr:uid="{0CC618F9-D07B-4A57-BB30-DA9D9C4F2552}"/>
+    <hyperlink ref="E5" r:id="rId55" location="org-chart" xr:uid="{4B9B4038-25F7-4818-A396-E389A8472AC5}"/>
+    <hyperlink ref="E6" r:id="rId56" xr:uid="{A28EE9FF-23D1-4089-A2E1-68FA61B83DF6}"/>
+    <hyperlink ref="E7" r:id="rId57" xr:uid="{EBF8C6EF-5F76-4B85-B16F-3C00DCF81CE8}"/>
+    <hyperlink ref="E8" r:id="rId58" xr:uid="{6E216DFF-697F-4D2E-8F78-1FEF1CEC39BD}"/>
+    <hyperlink ref="E10" r:id="rId59" xr:uid="{736C7E7B-A325-49CD-995B-BEA88AFBE739}"/>
+    <hyperlink ref="E11" r:id="rId60" xr:uid="{7FBF4A86-93BE-4208-85BD-4C057C9D0673}"/>
+    <hyperlink ref="E12" r:id="rId61" xr:uid="{55A76AD9-7045-45D5-9195-B69B42AF0802}"/>
+    <hyperlink ref="E14" r:id="rId62" xr:uid="{029BF59C-D9AF-4315-B2A4-78BE99C97F94}"/>
+    <hyperlink ref="E13" r:id="rId63" xr:uid="{3D68E0F6-565A-4E31-8041-14A4E4AAA026}"/>
+    <hyperlink ref="E16" r:id="rId64" xr:uid="{EF1D420F-18EF-4E76-89A3-98850C9AF20C}"/>
+    <hyperlink ref="E17" r:id="rId65" xr:uid="{F78DA305-9BB5-4F2E-B4F8-66EC8FBDDA3D}"/>
+    <hyperlink ref="E19" r:id="rId66" xr:uid="{34B32381-DA3D-48A1-8F3A-7BA553623903}"/>
+    <hyperlink ref="E20" r:id="rId67" xr:uid="{45465AA5-EEE0-48FC-9065-53047723500D}"/>
+    <hyperlink ref="E21" r:id="rId68" xr:uid="{13BB9942-A405-4DA2-8E06-01F90B4BD748}"/>
+    <hyperlink ref="E22" r:id="rId69" xr:uid="{DA4BEBE2-080E-4CD9-B20D-9A66E0B9BA0E}"/>
+    <hyperlink ref="E24" r:id="rId70" xr:uid="{9BAD52EC-0FBB-47D0-B299-98976A4A44C1}"/>
+    <hyperlink ref="E26" r:id="rId71" xr:uid="{BBB29648-EE03-4690-B8CF-7336712FAED6}"/>
+    <hyperlink ref="E27" r:id="rId72" xr:uid="{02DC2D59-84BF-4EEB-AE0B-79A2F174ED4E}"/>
+    <hyperlink ref="E28" r:id="rId73" xr:uid="{A63C04C4-8DD9-435D-ABF9-0203E47DF1B0}"/>
+    <hyperlink ref="E29" r:id="rId74" xr:uid="{8E647A81-A99D-4893-8BBE-EA2D0B10E098}"/>
+    <hyperlink ref="E31" r:id="rId75" xr:uid="{2E33A0D8-379C-435E-914F-1511B519A04E}"/>
+    <hyperlink ref="E32" r:id="rId76" xr:uid="{28D87A6B-7FF4-40B3-B258-618F4D30BC9B}"/>
+    <hyperlink ref="E34" r:id="rId77" xr:uid="{EB604F45-7F62-4D95-87A0-7C607F70EEE6}"/>
+    <hyperlink ref="E35" r:id="rId78" xr:uid="{FF0F238A-0D26-48C4-A15F-7954889B76EF}"/>
+    <hyperlink ref="E37" r:id="rId79" xr:uid="{6A9F5AC2-0769-4F65-A1B3-C7B6B78865CF}"/>
+    <hyperlink ref="E38" r:id="rId80" xr:uid="{8F8CC71E-CB4F-469E-8417-A15A6E522D48}"/>
+    <hyperlink ref="E39" r:id="rId81" xr:uid="{70588B6D-86C2-4E9D-A653-EB43F4458978}"/>
+    <hyperlink ref="E9" r:id="rId82" xr:uid="{2BC13BFC-19BE-477A-82E0-7D14CED900F5}"/>
+    <hyperlink ref="E40" r:id="rId83" xr:uid="{7A331BB3-C033-4479-BE55-986C3D9F9A53}"/>
+    <hyperlink ref="E41" r:id="rId84" xr:uid="{9D770BB2-4EC1-4C1B-9178-82ADFA28631B}"/>
+    <hyperlink ref="E42" r:id="rId85" xr:uid="{9BCD1D34-3807-4EFF-9AFB-1B2D272BAC40}"/>
+    <hyperlink ref="E43" r:id="rId86" xr:uid="{D7E4C853-E250-43E6-9D4D-F09FCBFF6B2F}"/>
+    <hyperlink ref="E44" r:id="rId87" xr:uid="{74D7670D-4811-4714-AC93-1B08F70715DA}"/>
+    <hyperlink ref="E46" r:id="rId88" xr:uid="{CB748B89-0123-4681-825A-E27A0BE8ECB1}"/>
+    <hyperlink ref="E48" r:id="rId89" xr:uid="{4D3EFA2A-19FF-4AD8-84E1-C8E13C595478}"/>
+    <hyperlink ref="E50" r:id="rId90" xr:uid="{A4C956F3-167F-4BD7-A91C-26AD208A0BD1}"/>
+    <hyperlink ref="E51" r:id="rId91" xr:uid="{1749D594-EE49-4E34-B8D1-987FAE0B65C9}"/>
+    <hyperlink ref="E53" r:id="rId92" xr:uid="{1380FF99-EF25-4839-8AF5-637A67A7D467}"/>
+    <hyperlink ref="E54" r:id="rId93" xr:uid="{4E15A300-DD30-44C2-BA8F-B49EEC02963B}"/>
+    <hyperlink ref="E55" r:id="rId94" xr:uid="{0F99CB0B-4B4B-4B69-9AC3-D56535324B5D}"/>
+    <hyperlink ref="E56" r:id="rId95" xr:uid="{D941B546-8A6E-4F9C-AEA8-DF3FB2FD1934}"/>
+    <hyperlink ref="E57" r:id="rId96" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
+    <hyperlink ref="E58" r:id="rId97" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
+    <hyperlink ref="F53" r:id="rId98" xr:uid="{435B592D-DD21-4EC5-9AFF-18B7F3BB085D}"/>
+    <hyperlink ref="F58" r:id="rId99" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
+    <hyperlink ref="F57" r:id="rId100" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
+    <hyperlink ref="E33" r:id="rId101" xr:uid="{25D99204-4613-42A1-BE9B-F2E5D561C894}"/>
+    <hyperlink ref="E18" r:id="rId102" xr:uid="{8F612C67-B290-475F-A329-18B4A1CD494F}"/>
+    <hyperlink ref="E30" r:id="rId103" xr:uid="{C9CED6DD-2DA0-41FC-871A-F66D82DD880B}"/>
+    <hyperlink ref="E36" r:id="rId104" xr:uid="{60B932FB-29EC-45F2-B889-1CB79A7CA2CB}"/>
+    <hyperlink ref="E47" r:id="rId105" xr:uid="{A29855BD-159B-419E-AEF2-13C042924D47}"/>
+    <hyperlink ref="E15" r:id="rId106" xr:uid="{8075B8C8-FB88-7B49-BD90-E19F35481EB2}"/>
+    <hyperlink ref="E49" r:id="rId107" xr:uid="{D13B153E-E756-3347-A1AB-AB3EE4BA2858}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId110"/>
+    <tablePart r:id="rId108"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -9217,6 +9218,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ArtifactsRequested_x003f_ xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">Yes</ArtifactsRequested_x003f_>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6f04fd38-88d0-493d-bcfe-f0680152bc54" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010067084DD94AAF9F49A29187A8281A736B" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31370f96594e886cf5a1a287283c7112">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e" xmlns:ns3="9843afbf-a983-44da-9ef0-770fe2475dd9" xmlns:ns4="6f04fd38-88d0-493d-bcfe-f0680152bc54" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd273aee41ba6857014841f4b535fddc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
@@ -9490,33 +9517,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E5FD91-6CDF-4778-8B48-65EB30B9BE76}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
+    <ds:schemaRef ds:uri="6f04fd38-88d0-493d-bcfe-f0680152bc54"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ArtifactsRequested_x003f_ xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">Yes</ArtifactsRequested_x003f_>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6f04fd38-88d0-493d-bcfe-f0680152bc54" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08ABF4CA-0893-4703-B384-163F0489B58B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9534,31 +9562,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E5FD91-6CDF-4778-8B48-65EB30B9BE76}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
-    <ds:schemaRef ds:uri="6f04fd38-88d0-493d-bcfe-f0680152bc54"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/updatedMemberData.xlsx
+++ b/updatedMemberData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madmarshall/Documents/medicaidOversightMap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65A340F-9EFD-5849-88C1-447E468EF906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B4BE4-EB0E-C846-8EB1-24581645C0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="960" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="13" t="s">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="B37" s="24" t="s">
         <v>463</v>

--- a/updatedMemberData.xlsx
+++ b/updatedMemberData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madmarshall/Documents/medicaidOversightMap/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madmarshall/Documents/01_ASTHO/03_HRSA-NOSLO/medicaidOversightMap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B4BE4-EB0E-C846-8EB1-24581645C0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718BADA5-9714-6742-9432-D4257B2E4DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="960" windowWidth="21400" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6040" yWindow="800" windowWidth="22160" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="507">
   <si>
     <t>Oversight?</t>
   </si>
@@ -1523,6 +1523,42 @@
   </si>
   <si>
     <t>https://www.chfs.ky.gov/services/Pages/search.aspx</t>
+  </si>
+  <si>
+    <t>Idaho Division of Public Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maryland Department of Health </t>
+  </si>
+  <si>
+    <t>https://health.maryland.gov/Pages/Home.aspx</t>
+  </si>
+  <si>
+    <t>MD-DOH</t>
+  </si>
+  <si>
+    <t>Seshamani, Meena</t>
+  </si>
+  <si>
+    <t>Sullivan, Meg</t>
+  </si>
+  <si>
+    <t>https://health.maryland.gov/iac/Documents/MDH%20Organization%20Chart%20-%20060525.pdf</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>New Hampshire Department of Health &amp; Human Services, Division of Public Health</t>
+  </si>
+  <si>
+    <t>Wisconsin Department of Health Services, Division of Public Health</t>
+  </si>
+  <si>
+    <t>Delaware Department of Health and Social Services, Division of Public Health</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1568,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -1548,6 +1584,11 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1606,7 +1647,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1693,12 +1734,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1729,6 +1781,9 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1863,10 +1918,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U58" totalsRowShown="0">
-  <autoFilter ref="A1:U58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U58">
-    <sortCondition ref="B1:B58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U59" totalsRowShown="0">
+  <autoFilter ref="A1:U59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U59">
+    <sortCondition ref="B1:B59"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="24" xr3:uid="{EC3A8AE4-1AEA-44FE-9DAE-C845A25235D5}" name="Oversight?" dataDxfId="13"/>
@@ -2246,7 +2301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="dataSheet"/>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="42.83203125" style="2" customWidth="1"/>
@@ -2842,7 +2897,7 @@
         <v>438</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>260</v>
@@ -3227,7 +3282,7 @@
         <v>445</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>260</v>
@@ -4137,7 +4192,7 @@
         <v>460</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>260</v>
@@ -4314,7 +4369,7 @@
         <v>146</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>147</v>
@@ -5130,7 +5185,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="B52" s="24" t="s">
         <v>480</v>
@@ -5139,7 +5194,7 @@
         <v>204</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>205</v>
@@ -5413,50 +5468,43 @@
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A57" s="15" t="s">
-        <v>258</v>
+      <c r="A57" s="21" t="s">
+        <v>309</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D57" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="D57" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>24</v>
+      <c r="E57" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="23" t="s">
+        <v>503</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I57" t="s">
-        <v>37</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>267</v>
+        <v>498</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="K57" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="O57" s="32" t="s">
+        <v>501</v>
+      </c>
+      <c r="P57" s="30" t="s">
+        <v>499</v>
       </c>
       <c r="Q57" s="3">
-        <v>5822434</v>
+        <v>6265347</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>30</v>
@@ -5465,108 +5513,167 @@
         <v>219</v>
       </c>
       <c r="T57" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="U57" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
         <v>258</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>417</v>
+        <v>505</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>260</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>418</v>
+        <v>261</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>419</v>
+        <v>262</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>420</v>
+        <v>263</v>
       </c>
       <c r="I58" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>422</v>
+        <v>264</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>423</v>
+        <v>266</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>418</v>
+        <v>261</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>424</v>
+        <v>267</v>
       </c>
       <c r="Q58" s="3">
-        <v>578759</v>
+        <v>5822434</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="S58" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="T58" t="s">
         <v>32</v>
       </c>
       <c r="U58" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I59" t="s">
+        <v>168</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>578759</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S59" t="s">
+        <v>71</v>
+      </c>
+      <c r="T59" t="s">
+        <v>32</v>
+      </c>
+      <c r="U59" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A59" s="26"/>
-      <c r="E59" s="25"/>
-    </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A60" s="27"/>
+      <c r="A60" s="26"/>
       <c r="E60" s="25"/>
     </row>
-    <row r="61" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A61" s="27"/>
       <c r="E61" s="25"/>
+    </row>
+    <row r="62" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28"/>
+      <c r="E62" s="25"/>
     </row>
   </sheetData>
   <dataValidations xWindow="185" yWindow="923" count="12">
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 20 characters long." promptTitle="Text" prompt="Maximum Length: 20 characters." sqref="H2:H58 I59:I1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 20 characters long." promptTitle="Text" prompt="Maximum Length: 20 characters." sqref="H2:H59 I60:I1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>20</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 160 characters long." promptTitle="Text (required)" prompt="Maximum Length: 160 characters." sqref="C2:C58" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 160 characters long." promptTitle="Text (required)" prompt="Maximum Length: 160 characters." sqref="C2:C56 C58:C59" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>160</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="MultiSelect Option set" prompt="Enter Option Set values as semicolon separated." sqref="I2:I58 S2:U58 T59:V1048576 H59:J1048576" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO record must already exist in Microsoft Dynamics 365 or in this source file." sqref="J2:J58 K59:K1048576" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Designee record must already exist in Microsoft Dynamics 365 or in this source file." sqref="K2:K58 L59:L1048576" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Acting record must already exist in Microsoft Dynamics 365 or in this source file." sqref="L2:L58 M59:M1048576" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Assistant record must already exist in Microsoft Dynamics 365 or in this source file." sqref="M2:M58 N59:N1048576" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 80 characters long." promptTitle="Text" prompt="Maximum Length: 80 characters." sqref="N2:N58 O59:O1048576" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="MultiSelect Option set" prompt="Enter Option Set values as semicolon separated." sqref="I2:I59 S2:U59 T60:V1048576 H60:J1048576" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO record must already exist in Microsoft Dynamics 365 or in this source file." sqref="K60:K1048576 J2:J56 J58:J59" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Designee record must already exist in Microsoft Dynamics 365 or in this source file." sqref="L60:L1048576 K2:K56 K58:K59" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Acting record must already exist in Microsoft Dynamics 365 or in this source file." sqref="L2:L59 M60:M1048576" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This S/THO Assistant record must already exist in Microsoft Dynamics 365 or in this source file." sqref="M2:M59 N60:N1048576" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 80 characters long." promptTitle="Text" prompt="Maximum Length: 80 characters." sqref="N2:N59 O60:O1048576" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>80</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 200 characters long." promptTitle="Text" prompt="Maximum Length: 200 characters." sqref="E2:F58 O2:O58 P59:P1048576" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 200 characters long." promptTitle="Text" prompt="Maximum Length: 200 characters." sqref="P60:P1048576 E58:E59 F2:F59 E2:E56 O2:O56 O58:O59" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>200</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This Secretary of Health record must already exist in Microsoft Dynamics 365 or in this source file." sqref="P2:P58 Q59:Q1048576" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value beyond range" error="Population must be a whole number from 0 through 2147483647." promptTitle="Whole number" prompt="Minimum Value: 0._x000d__x000a_Maximum Value: 2147483647._x000d__x000a_  " sqref="Q2:Q58 R59:R1048576" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error=" " promptTitle="Lookup" prompt="This Secretary of Health record must already exist in Microsoft Dynamics 365 or in this source file." sqref="Q60:Q1048576 P2:P56 P58:P59" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value beyond range" error="Population must be a whole number from 0 through 2147483647." promptTitle="Whole number" prompt="Minimum Value: 0._x000d__x000a_Maximum Value: 2147483647._x000d__x000a_  " sqref="Q2:Q59 R60:R1048576" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 4 characters long." promptTitle="Text" prompt="Maximum Length: 4 characters." sqref="G2:G58 F59:F1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Length Exceeded" error="This value must be less than or equal to 4 characters long." promptTitle="Text" prompt="Maximum Length: 4 characters." sqref="G2:G59 F60:F1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>4</formula1>
     </dataValidation>
   </dataValidations>
@@ -5620,8 +5727,8 @@
     <hyperlink ref="O54" r:id="rId47" xr:uid="{D7B0DACD-5FD1-4346-B4E7-958EFDE6DA7C}"/>
     <hyperlink ref="O55" r:id="rId48" xr:uid="{55EB6149-0908-4B53-A043-978695B6AFF2}"/>
     <hyperlink ref="O56" r:id="rId49" xr:uid="{566E4284-EA29-42AE-ADF0-6D11CA2D7918}"/>
-    <hyperlink ref="O57" r:id="rId50" xr:uid="{1F555AFE-78CF-4F3C-9D4D-8A9484A22E05}"/>
-    <hyperlink ref="O58" r:id="rId51" xr:uid="{A07AD047-9BF8-4A20-B9F9-4A6749EA616A}"/>
+    <hyperlink ref="O58" r:id="rId50" xr:uid="{1F555AFE-78CF-4F3C-9D4D-8A9484A22E05}"/>
+    <hyperlink ref="O59" r:id="rId51" xr:uid="{A07AD047-9BF8-4A20-B9F9-4A6749EA616A}"/>
     <hyperlink ref="E2" r:id="rId52" xr:uid="{FEE37E5B-198F-4348-8CCA-D7ED5F656AAC}"/>
     <hyperlink ref="E3" r:id="rId53" xr:uid="{03D7C8ED-BBB4-45E8-BC5C-86ACD2650E41}"/>
     <hyperlink ref="E4" r:id="rId54" xr:uid="{0CC618F9-D07B-4A57-BB30-DA9D9C4F2552}"/>
@@ -5666,11 +5773,11 @@
     <hyperlink ref="E54" r:id="rId93" xr:uid="{4E15A300-DD30-44C2-BA8F-B49EEC02963B}"/>
     <hyperlink ref="E55" r:id="rId94" xr:uid="{0F99CB0B-4B4B-4B69-9AC3-D56535324B5D}"/>
     <hyperlink ref="E56" r:id="rId95" xr:uid="{D941B546-8A6E-4F9C-AEA8-DF3FB2FD1934}"/>
-    <hyperlink ref="E57" r:id="rId96" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
-    <hyperlink ref="E58" r:id="rId97" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
+    <hyperlink ref="E58" r:id="rId96" xr:uid="{4F41EEAE-E6DF-4432-A83D-08B8DBD75934}"/>
+    <hyperlink ref="E59" r:id="rId97" xr:uid="{1E3794A4-06A0-428E-B3C5-B6CF6637ACB4}"/>
     <hyperlink ref="F53" r:id="rId98" xr:uid="{435B592D-DD21-4EC5-9AFF-18B7F3BB085D}"/>
-    <hyperlink ref="F58" r:id="rId99" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
-    <hyperlink ref="F57" r:id="rId100" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
+    <hyperlink ref="F59" r:id="rId99" xr:uid="{9242EECC-BD31-44D9-90EB-51E2B0A20F91}"/>
+    <hyperlink ref="F58" r:id="rId100" xr:uid="{E6226532-F402-4D02-8A51-FC5F911E486B}"/>
     <hyperlink ref="E33" r:id="rId101" xr:uid="{25D99204-4613-42A1-BE9B-F2E5D561C894}"/>
     <hyperlink ref="E18" r:id="rId102" xr:uid="{8F612C67-B290-475F-A329-18B4A1CD494F}"/>
     <hyperlink ref="E30" r:id="rId103" xr:uid="{C9CED6DD-2DA0-41FC-871A-F66D82DD880B}"/>
@@ -5678,10 +5785,12 @@
     <hyperlink ref="E47" r:id="rId105" xr:uid="{A29855BD-159B-419E-AEF2-13C042924D47}"/>
     <hyperlink ref="E15" r:id="rId106" xr:uid="{8075B8C8-FB88-7B49-BD90-E19F35481EB2}"/>
     <hyperlink ref="E49" r:id="rId107" xr:uid="{D13B153E-E756-3347-A1AB-AB3EE4BA2858}"/>
+    <hyperlink ref="E57" r:id="rId108" xr:uid="{3364B68C-0A03-B94D-9B32-7FFC45828012}"/>
+    <hyperlink ref="O57" r:id="rId109" display="https://health.maryland.gov/iac/Documents/MDH Organization Chart - 060525.pdf" xr:uid="{B213A2ED-7407-3440-A577-14A61D6B769E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId108"/>
+    <tablePart r:id="rId110"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -5690,13 +5799,13 @@
           <x14:formula1>
             <xm:f>hiddenSheet!$A$2:$C$2</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:H58 J59:J1048576</xm:sqref>
+          <xm:sqref>J60:J1048576 F2:H59 D58:E59 D2:E56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="List Value" error="PHAB Accreditation must be selected from the drop-down list." promptTitle="Option set" prompt="Select a value from the drop-down list." xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
             <xm:f>hiddenSheet!$A$3:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>R2:R58 S59:S1048576</xm:sqref>
+          <xm:sqref>R2:R59 S60:S1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9218,6 +9327,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ArtifactsRequested_x003f_ xmlns="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e">Yes</ArtifactsRequested_x003f_>
@@ -9229,21 +9347,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010067084DD94AAF9F49A29187A8281A736B" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31370f96594e886cf5a1a287283c7112">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e" xmlns:ns3="9843afbf-a983-44da-9ef0-770fe2475dd9" xmlns:ns4="6f04fd38-88d0-493d-bcfe-f0680152bc54" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd273aee41ba6857014841f4b535fddc" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c6cb7c5a-edb7-416a-adb1-0d17ade57b9e"/>
@@ -9517,7 +9621,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="c3a201dd-47de-4cb5-b1b8-fb4eacb25aeb" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E5FD91-6CDF-4778-8B48-65EB30B9BE76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9528,23 +9645,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C0E0DC-1A45-4E37-9177-6BF15AAC155D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08ABF4CA-0893-4703-B384-163F0489B58B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9562,4 +9663,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2749A39F-5866-4570-A7EA-0749A01EC9F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>